--- a/tame_output/ON/bt/strategyON_20240124.xlsx
+++ b/tame_output/ON/bt/strategyON_20240124.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-23</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-5.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-23</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.0%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>1.4%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-23</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>451.3%</t>
+          <t>451.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>3.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.2%</t>
+          <t>101.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>95.5%</t>
+          <t>96.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-18.7%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>2.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>2.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>129.3%</t>
+          <t>130.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,16 +1400,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-22</t>
+          <t>2024-01-23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>124.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.4%</t>
+          <t>2.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1851"/>
+  <dimension ref="A1:G1852"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23611727413042</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44134,6 +44134,29 @@
       </c>
       <c r="G1851" t="n">
         <v>4.464474930318332</v>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" s="2" t="n">
+        <v>45314</v>
+      </c>
+      <c r="B1852" t="n">
+        <v>3.223829153706125</v>
+      </c>
+      <c r="C1852" t="n">
+        <v>3.130342856487082</v>
+      </c>
+      <c r="D1852" t="n">
+        <v>1.650112151748115</v>
+      </c>
+      <c r="E1852" t="n">
+        <v>3.79003129287258</v>
+      </c>
+      <c r="F1852" t="n">
+        <v>2.264522789656479</v>
+      </c>
+      <c r="G1852" t="n">
+        <v>4.48905653028097</v>
       </c>
     </row>
   </sheetData>
